--- a/Catologo de Servicios Matilde360 (1).xlsx
+++ b/Catologo de Servicios Matilde360 (1).xlsx
@@ -605,7 +605,7 @@
   <sheetPr>
     <tabColor rgb="FF1B2A4A"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -927,6 +927,93 @@
         <v>35</v>
       </c>
     </row>
+    <row r="18" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="20">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Diseño de marbetes (envase primario)</t>
+        </is>
+      </c>
+      <c r="C18" s="12">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="12">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Por proyecto</t>
+        </is>
+      </c>
+      <c r="F18" s="14">
+        <v>0.65</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Diseño de marbetes para envase primario</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>9</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Diseño de cajas plegadizas (envase secundario)</t>
+        </is>
+      </c>
+      <c r="C19" s="9">
+        <v>4000</v>
+      </c>
+      <c r="D19" s="9">
+        <v>4000</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Por proyecto</t>
+        </is>
+      </c>
+      <c r="F19" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Diseño de cajas plegadizas para envase secundario</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="20">
+        <v>10</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Diseño de instructivo</t>
+        </is>
+      </c>
+      <c r="C20" s="12">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Por proyecto</t>
+        </is>
+      </c>
+      <c r="F20" s="14">
+        <v>0.65</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Diseño de instructivo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
